--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,22 +454,37 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>cast_time_ticks</t>
+          <t>startup_ticks</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>active_ticks</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recovery_ticks</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>targeting_mode</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>produces_effect_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>motion_speed</t>
         </is>
       </c>
     </row>
@@ -516,17 +531,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -550,6 +580,9 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,22 +622,37 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cast_time_ticks</t>
+          <t>startup_ticks</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>active_ticks</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>recovery_ticks</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>targeting_mode</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>produces_effect_id</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>motion_speed</t>
         </is>
       </c>
     </row>
@@ -637,16 +685,75 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dash</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dash</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>전방 대시</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>targeting_mode</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>produces_effect_id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>motion_speed</t>
+          <t>effects#sep=,</t>
         </is>
       </c>
     </row>
@@ -541,22 +526,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>float</t>
+          <t>list,AbilityEffect</t>
         </is>
       </c>
     </row>
@@ -566,23 +536,11 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -637,27 +595,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>targeting_mode</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>produces_effect_id</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>motion_speed</t>
+          <t>effects</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
         <v>1</v>
       </c>
@@ -693,21 +635,11 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
+          <t>StatusEffectApplyEffect,1</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>2</v>
       </c>
@@ -736,24 +668,55 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15</v>
+          <t>MotionEffect,15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>근접 공격 (부채꼴)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>DamageEffect,10,2,90</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>cue</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>effects#sep=,</t>
         </is>
       </c>
@@ -526,6 +531,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>list,AbilityEffect</t>
         </is>
       </c>
@@ -541,6 +551,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,6 +609,11 @@
         </is>
       </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>cue</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>effects</t>
         </is>
@@ -633,7 +653,8 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>StatusEffectApplyEffect,1</t>
         </is>
@@ -673,7 +694,8 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>MotionEffect,15</t>
         </is>
@@ -714,6 +736,11 @@
         <v>18</v>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>DamageEffect,10,2,90</t>
         </is>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -653,7 +653,6 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>StatusEffectApplyEffect,1</t>
@@ -694,7 +693,6 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>MotionEffect,15</t>
@@ -742,7 +740,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DamageEffect,10,2,90</t>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,2,90,12,0.8</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,26 @@
           <t>effects#sep=,</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>startup_move_scale</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>active_move_scale</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>recovery_move_scale</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>block_jump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +559,26 @@
           <t>list,AbilityEffect</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,6 +656,26 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>effects</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>startup_move_scale</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>active_move_scale</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>recovery_move_scale</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>block_jump</t>
         </is>
       </c>
     </row>
@@ -658,6 +718,20 @@
           <t>StatusEffectApplyEffect,1</t>
         </is>
       </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -698,6 +772,20 @@
           <t>MotionEffect,15</t>
         </is>
       </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -741,6 +829,20 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>DamageEffect,10,2,90,KnockbackEffect,5,2,90,12,0.8</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -828,7 +828,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DamageEffect,10,2,90,KnockbackEffect,5,2,90,12,0.8</t>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
         </is>
       </c>
       <c r="M7" t="n">

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,6 +843,65 @@
       <c r="P7" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>global_attack</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>global_attack</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>전역 공격 (테스트용)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DamageEffect,30,30,360</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,128 @@
       <c r="P8" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>necro_attack</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>necro_attack</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>근접 공격 (부채꼴)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>archer_attack</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>archer_attack</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>근접 공격 (부채꼴)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,30 +469,25 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>cue</t>
+          <t>effects#sep=,</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>effects#sep=,</t>
+          <t>startup_move_scale</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>startup_move_scale</t>
+          <t>active_move_scale</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>active_move_scale</t>
+          <t>recovery_move_scale</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>recovery_move_scale</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>block_jump</t>
         </is>
@@ -551,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>list,AbilityEffect</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>list,AbilityEffect</t>
+          <t>float</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -570,11 +565,6 @@
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
@@ -591,11 +581,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -650,30 +635,25 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>cue</t>
+          <t>effects</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>effects</t>
+          <t>startup_move_scale</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>startup_move_scale</t>
+          <t>active_move_scale</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>active_move_scale</t>
+          <t>recovery_move_scale</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>recovery_move_scale</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>block_jump</t>
         </is>
@@ -713,21 +693,21 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>StatusEffectApplyEffect,1</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -767,21 +747,21 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>MotionEffect,15</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -823,24 +803,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -882,24 +857,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
           <t>DamageEffect,30,30,360</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -943,24 +913,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
           <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -1004,24 +969,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
           <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>true</t>
         </is>

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -695,7 +695,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>StatusEffectApplyEffect,1</t>
+          <t>StatusEffectApplyEffect,1,Self</t>
         </is>
       </c>
       <c r="L5" t="n">

--- a/table/Datas/#Ability.xlsx
+++ b/table/Datas/#Ability.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8,StatusEffectApplyEffect,2,HitTargets</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8,StatusEffectApplyEffect,2,HitTargets</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8</t>
+          <t>DamageEffect,10,2,90,KnockbackEffect,5,12,0.8,StatusEffectApplyEffect,2,HitTargets</t>
         </is>
       </c>
       <c r="L10" t="n">
